--- a/Hand_edited_log/4/StudentsSolution.xlsx
+++ b/Hand_edited_log/4/StudentsSolution.xlsx
@@ -73,100 +73,160 @@
     <x:t>5</x:t>
   </x:si>
   <x:si>
+    <x:t>chucvvhe150977</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6</x:t>
+  </x:si>
+  <x:si>
     <x:t>duchvhe181827</x:t>
   </x:si>
   <x:si>
-    <x:t>6</x:t>
+    <x:t>7</x:t>
   </x:si>
   <x:si>
     <x:t>ducmhhs173341</x:t>
   </x:si>
   <x:si>
-    <x:t>7</x:t>
+    <x:t>8</x:t>
   </x:si>
   <x:si>
     <x:t>dunghdhe153770</x:t>
   </x:si>
   <x:si>
-    <x:t>8</x:t>
+    <x:t>9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dungnqhe186457</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dungtmhe181358</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
   </x:si>
   <x:si>
     <x:t>duypqhe172390</x:t>
   </x:si>
   <x:si>
-    <x:t>9</x:t>
+    <x:t>12</x:t>
   </x:si>
   <x:si>
     <x:t>giangvthe187264</x:t>
   </x:si>
   <x:si>
-    <x:t>10</x:t>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hailndhe182237</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>hanhnxhe180944</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
   </x:si>
   <x:si>
     <x:t>hoclhhe176114</x:t>
   </x:si>
   <x:si>
-    <x:t>11</x:t>
+    <x:t>16</x:t>
   </x:si>
   <x:si>
     <x:t>khanhnqhe173521</x:t>
   </x:si>
   <x:si>
-    <x:t>12</x:t>
+    <x:t>17</x:t>
   </x:si>
   <x:si>
     <x:t>namhdhe173231</x:t>
   </x:si>
   <x:si>
-    <x:t>13</x:t>
+    <x:t>18</x:t>
   </x:si>
   <x:si>
     <x:t>nhattmhe181227</x:t>
   </x:si>
   <x:si>
-    <x:t>14</x:t>
+    <x:t>19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>quanghvhe161464</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20</x:t>
   </x:si>
   <x:si>
     <x:t>sonnhhe186392</x:t>
   </x:si>
   <x:si>
-    <x:t>15</x:t>
+    <x:t>21</x:t>
   </x:si>
   <x:si>
     <x:t>ThaoDPHE176894</x:t>
   </x:si>
   <x:si>
-    <x:t>16</x:t>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>thaonthe151260</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23</x:t>
   </x:si>
   <x:si>
     <x:t>thientdhe163943</x:t>
   </x:si>
   <x:si>
-    <x:t>17</x:t>
+    <x:t>24</x:t>
   </x:si>
   <x:si>
     <x:t>thinhndhe186687</x:t>
   </x:si>
   <x:si>
-    <x:t>18</x:t>
+    <x:t>25</x:t>
   </x:si>
   <x:si>
     <x:t>trapche186790</x:t>
   </x:si>
   <x:si>
-    <x:t>19</x:t>
+    <x:t>26</x:t>
   </x:si>
   <x:si>
     <x:t>truongdhhe187014</x:t>
   </x:si>
   <x:si>
-    <x:t>20</x:t>
+    <x:t>27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>truongpqhe172222</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28</x:t>
+  </x:si>
+  <x:si>
+    <x:t>truongvxhe187103</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29</x:t>
   </x:si>
   <x:si>
     <x:t>tuanvhhe182160</x:t>
   </x:si>
   <x:si>
-    <x:t>21</x:t>
+    <x:t>30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tungdthe181764</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31</x:t>
   </x:si>
   <x:si>
     <x:t>vietvhhe170993</x:t>
@@ -540,7 +600,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G22"/>
+  <x:dimension ref="A1:G32"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="3.424911" style="0" customWidth="1"/>
@@ -1058,6 +1118,236 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
+    <x:row r="23" spans="1:7">
+      <x:c r="A23" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="B23" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C23" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E23" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F23" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G23" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:7">
+      <x:c r="A24" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B24" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C24" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D24" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E24" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F24" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G24" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:7">
+      <x:c r="A25" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B25" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="C25" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D25" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E25" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F25" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G25" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:7">
+      <x:c r="A26" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B26" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="C26" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D26" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E26" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F26" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G26" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:7">
+      <x:c r="A27" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E27" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F27" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G27" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:7">
+      <x:c r="A28" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E28" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F28" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G28" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:7">
+      <x:c r="A29" s="0" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E29" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F29" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G29" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:7">
+      <x:c r="A30" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D30" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E30" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F30" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G30" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:7">
+      <x:c r="A31" s="0" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E31" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F31" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G31" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:7">
+      <x:c r="A32" s="0" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D32" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E32" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F32" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G32" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
